--- a/data/csv/数据_==_1787048390520.xlsx
+++ b/data/csv/数据_==_1787048390520.xlsx
@@ -7861,7 +7861,7 @@
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
@@ -7882,7 +7882,7 @@
         <v>秒数(s)</v>
       </c>
       <c r="C1" t="str">
-        <v>框选坐标(JSON)</v>
+        <v>框选坐标</v>
       </c>
       <c r="D1" t="str">
         <v>上身框选1最大压强(N/cm²)</v>
@@ -7923,7 +7923,7 @@
         <v>0.000</v>
       </c>
       <c r="C2" t="str">
-        <v>{"key":"endi-jacket","xStart":6,"xEnd":12,"yStart":5,"yEnd":10,"width":24,"height":54,"name":"框选1","colorIndex":0}</v>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D2" t="str">
         <v>0.14</v>
@@ -7964,7 +7964,7 @@
         <v>0.084</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D3" t="str">
         <v>0.13</v>
@@ -8005,7 +8005,7 @@
         <v>0.166</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D4" t="str">
         <v>0.13</v>
@@ -8046,7 +8046,7 @@
         <v>0.249</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D5" t="str">
         <v>0.14</v>
@@ -8087,7 +8087,7 @@
         <v>0.333</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D6" t="str">
         <v>0.12</v>
@@ -8128,7 +8128,7 @@
         <v>0.415</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D7" t="str">
         <v>0.08</v>
@@ -8169,7 +8169,7 @@
         <v>0.499</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D8" t="str">
         <v>0.05</v>
@@ -8210,7 +8210,7 @@
         <v>0.582</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D9" t="str">
         <v>0.04</v>
@@ -8251,7 +8251,7 @@
         <v>0.664</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D10" t="str">
         <v>0.06</v>
@@ -8292,7 +8292,7 @@
         <v>0.747</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D11" t="str">
         <v>0.12</v>
@@ -8333,7 +8333,7 @@
         <v>0.831</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D12" t="str">
         <v>0.12</v>
@@ -8374,7 +8374,7 @@
         <v>0.913</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D13" t="str">
         <v>0.10</v>
@@ -8415,7 +8415,7 @@
         <v>0.997</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D14" t="str">
         <v>0.06</v>
@@ -8456,7 +8456,7 @@
         <v>1.080</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D15" t="str">
         <v>0.08</v>
@@ -8497,7 +8497,7 @@
         <v>1.162</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D16" t="str">
         <v>0.13</v>
@@ -8538,7 +8538,7 @@
         <v>1.244</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D17" t="str">
         <v>0.15</v>
@@ -8579,7 +8579,7 @@
         <v>1.328</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D18" t="str">
         <v>0.16</v>
@@ -8620,7 +8620,7 @@
         <v>1.411</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D19" t="str">
         <v>0.17</v>
@@ -8661,7 +8661,7 @@
         <v>1.494</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D20" t="str">
         <v>0.09</v>
@@ -8702,7 +8702,7 @@
         <v>1.576</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D21" t="str">
         <v>0.15</v>
@@ -8743,7 +8743,7 @@
         <v>1.660</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D22" t="str">
         <v>0.09</v>
@@ -8784,7 +8784,7 @@
         <v>1.743</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D23" t="str">
         <v>0.10</v>
@@ -8825,7 +8825,7 @@
         <v>1.826</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D24" t="str">
         <v>0.20</v>
@@ -8866,7 +8866,7 @@
         <v>1.910</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D25" t="str">
         <v>0.27</v>
@@ -8907,7 +8907,7 @@
         <v>1.990</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D26" t="str">
         <v>0.30</v>
@@ -8948,7 +8948,7 @@
         <v>2.076</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D27" t="str">
         <v>0.32</v>
@@ -8989,7 +8989,7 @@
         <v>2.159</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D28" t="str">
         <v>0.34</v>
@@ -9030,7 +9030,7 @@
         <v>2.240</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D29" t="str">
         <v>0.32</v>
@@ -9071,7 +9071,7 @@
         <v>2.325</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D30" t="str">
         <v>0.28</v>
@@ -9112,7 +9112,7 @@
         <v>2.407</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D31" t="str">
         <v>0.28</v>
@@ -9153,7 +9153,7 @@
         <v>2.491</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D32" t="str">
         <v>0.22</v>
@@ -9194,7 +9194,7 @@
         <v>2.573</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D33" t="str">
         <v>0.22</v>
@@ -9235,7 +9235,7 @@
         <v>2.656</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D34" t="str">
         <v>0.23</v>
@@ -9276,7 +9276,7 @@
         <v>2.739</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D35" t="str">
         <v>0.29</v>
@@ -9317,7 +9317,7 @@
         <v>2.823</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D36" t="str">
         <v>0.29</v>
@@ -9358,7 +9358,7 @@
         <v>2.905</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D37" t="str">
         <v>0.29</v>
@@ -9399,7 +9399,7 @@
         <v>2.988</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D38" t="str">
         <v>0.29</v>
@@ -9440,7 +9440,7 @@
         <v>3.071</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D39" t="str">
         <v>0.29</v>
@@ -9481,7 +9481,7 @@
         <v>3.152</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D40" t="str">
         <v>0.28</v>
@@ -9522,7 +9522,7 @@
         <v>3.237</v>
       </c>
       <c r="C41" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D41" t="str">
         <v>0.28</v>
@@ -9563,7 +9563,7 @@
         <v>3.320</v>
       </c>
       <c r="C42" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D42" t="str">
         <v>0.28</v>
@@ -9604,7 +9604,7 @@
         <v>3.403</v>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D43" t="str">
         <v>0.28</v>
@@ -9645,7 +9645,7 @@
         <v>3.483</v>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D44" t="str">
         <v>0.28</v>
@@ -9686,7 +9686,7 @@
         <v>3.570</v>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D45" t="str">
         <v>0.28</v>
@@ -9727,7 +9727,7 @@
         <v>3.652</v>
       </c>
       <c r="C46" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D46" t="str">
         <v>0.28</v>
@@ -9768,7 +9768,7 @@
         <v>3.735</v>
       </c>
       <c r="C47" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D47" t="str">
         <v>0.28</v>
@@ -9809,7 +9809,7 @@
         <v>3.818</v>
       </c>
       <c r="C48" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D48" t="str">
         <v>0.28</v>
@@ -9850,7 +9850,7 @@
         <v>3.902</v>
       </c>
       <c r="C49" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D49" t="str">
         <v>0.28</v>
@@ -9891,7 +9891,7 @@
         <v>3.984</v>
       </c>
       <c r="C50" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D50" t="str">
         <v>0.28</v>
@@ -9932,7 +9932,7 @@
         <v>4.067</v>
       </c>
       <c r="C51" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D51" t="str">
         <v>0.28</v>
@@ -9973,7 +9973,7 @@
         <v>4.150</v>
       </c>
       <c r="C52" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D52" t="str">
         <v>0.27</v>
@@ -10014,7 +10014,7 @@
         <v>4.232</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D53" t="str">
         <v>0.28</v>
@@ -10055,7 +10055,7 @@
         <v>4.316</v>
       </c>
       <c r="C54" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D54" t="str">
         <v>0.28</v>
@@ -10096,7 +10096,7 @@
         <v>4.399</v>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D55" t="str">
         <v>0.28</v>
@@ -10137,7 +10137,7 @@
         <v>4.483</v>
       </c>
       <c r="C56" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D56" t="str">
         <v>0.28</v>
@@ -10178,7 +10178,7 @@
         <v>4.565</v>
       </c>
       <c r="C57" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D57" t="str">
         <v>0.27</v>
@@ -10219,7 +10219,7 @@
         <v>4.648</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D58" t="str">
         <v>0.27</v>
@@ -10260,7 +10260,7 @@
         <v>4.731</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D59" t="str">
         <v>0.27</v>
@@ -10301,7 +10301,7 @@
         <v>4.814</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D60" t="str">
         <v>0.27</v>
@@ -10342,7 +10342,7 @@
         <v>4.898</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D61" t="str">
         <v>0.27</v>
@@ -10383,7 +10383,7 @@
         <v>4.981</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D62" t="str">
         <v>0.27</v>
@@ -10424,7 +10424,7 @@
         <v>5.061</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D63" t="str">
         <v>0.27</v>
@@ -10465,7 +10465,7 @@
         <v>5.147</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D64" t="str">
         <v>0.26</v>
@@ -10506,7 +10506,7 @@
         <v>5.228</v>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D65" t="str">
         <v>0.26</v>
@@ -10547,7 +10547,7 @@
         <v>5.312</v>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D66" t="str">
         <v>0.26</v>
@@ -10588,7 +10588,7 @@
         <v>5.394</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D67" t="str">
         <v>0.26</v>
@@ -10629,7 +10629,7 @@
         <v>5.478</v>
       </c>
       <c r="C68" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D68" t="str">
         <v>0.26</v>
@@ -10670,7 +10670,7 @@
         <v>5.561</v>
       </c>
       <c r="C69" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D69" t="str">
         <v>0.26</v>
@@ -10711,7 +10711,7 @@
         <v>5.645</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D70" t="str">
         <v>0.26</v>
@@ -10752,7 +10752,7 @@
         <v>5.727</v>
       </c>
       <c r="C71" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D71" t="str">
         <v>0.26</v>
@@ -10793,7 +10793,7 @@
         <v>5.810</v>
       </c>
       <c r="C72" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D72" t="str">
         <v>0.26</v>
@@ -10834,7 +10834,7 @@
         <v>5.894</v>
       </c>
       <c r="C73" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D73" t="str">
         <v>0.26</v>
@@ -10875,7 +10875,7 @@
         <v>5.975</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D74" t="str">
         <v>0.26</v>
@@ -10916,7 +10916,7 @@
         <v>6.059</v>
       </c>
       <c r="C75" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D75" t="str">
         <v>0.26</v>
@@ -10957,7 +10957,7 @@
         <v>6.144</v>
       </c>
       <c r="C76" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D76" t="str">
         <v>0.26</v>
@@ -10998,7 +10998,7 @@
         <v>6.225</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D77" t="str">
         <v>0.26</v>
@@ -11039,7 +11039,7 @@
         <v>6.308</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>(5, 6) (5, 11) (9, 11) (9, 6)</v>
       </c>
       <c r="D78" t="str">
         <v>0.26</v>
@@ -11085,7 +11085,7 @@
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
@@ -11106,7 +11106,7 @@
         <v>秒数(s)</v>
       </c>
       <c r="C1" t="str">
-        <v>框选坐标(JSON)</v>
+        <v>框选坐标</v>
       </c>
       <c r="D1" t="str">
         <v>上身框选2最大压强(N/cm²)</v>
@@ -11147,7 +11147,7 @@
         <v>0.000</v>
       </c>
       <c r="C2" t="str">
-        <v>{"key":"endi-jacket","xStart":1,"xEnd":6,"yStart":16,"yEnd":20,"width":24,"height":54,"name":"框选2","colorIndex":1}</v>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D2" t="str">
         <v>0.12</v>
@@ -11188,7 +11188,7 @@
         <v>0.084</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D3" t="str">
         <v>0.12</v>
@@ -11229,7 +11229,7 @@
         <v>0.166</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D4" t="str">
         <v>0.12</v>
@@ -11270,7 +11270,7 @@
         <v>0.249</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D5" t="str">
         <v>0.12</v>
@@ -11311,7 +11311,7 @@
         <v>0.333</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D6" t="str">
         <v>0.12</v>
@@ -11352,7 +11352,7 @@
         <v>0.415</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D7" t="str">
         <v>0.12</v>
@@ -11393,7 +11393,7 @@
         <v>0.499</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D8" t="str">
         <v>0.11</v>
@@ -11434,7 +11434,7 @@
         <v>0.582</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D9" t="str">
         <v>0.11</v>
@@ -11475,7 +11475,7 @@
         <v>0.664</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D10" t="str">
         <v>0.11</v>
@@ -11516,7 +11516,7 @@
         <v>0.747</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D11" t="str">
         <v>0.11</v>
@@ -11557,7 +11557,7 @@
         <v>0.831</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D12" t="str">
         <v>0.11</v>
@@ -11598,7 +11598,7 @@
         <v>0.913</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D13" t="str">
         <v>0.11</v>
@@ -11639,7 +11639,7 @@
         <v>0.997</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D14" t="str">
         <v>0.16</v>
@@ -11680,7 +11680,7 @@
         <v>1.080</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D15" t="str">
         <v>0.15</v>
@@ -11721,7 +11721,7 @@
         <v>1.162</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D16" t="str">
         <v>0.15</v>
@@ -11762,7 +11762,7 @@
         <v>1.244</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D17" t="str">
         <v>0.16</v>
@@ -11803,7 +11803,7 @@
         <v>1.328</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D18" t="str">
         <v>0.17</v>
@@ -11844,7 +11844,7 @@
         <v>1.411</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D19" t="str">
         <v>0.16</v>
@@ -11885,7 +11885,7 @@
         <v>1.494</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D20" t="str">
         <v>0.15</v>
@@ -11926,7 +11926,7 @@
         <v>1.576</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D21" t="str">
         <v>0.14</v>
@@ -11967,7 +11967,7 @@
         <v>1.660</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D22" t="str">
         <v>0.12</v>
@@ -12008,7 +12008,7 @@
         <v>1.743</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D23" t="str">
         <v>0.15</v>
@@ -12049,7 +12049,7 @@
         <v>1.826</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D24" t="str">
         <v>0.16</v>
@@ -12090,7 +12090,7 @@
         <v>1.910</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D25" t="str">
         <v>0.16</v>
@@ -12131,7 +12131,7 @@
         <v>1.990</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D26" t="str">
         <v>0.17</v>
@@ -12172,7 +12172,7 @@
         <v>2.076</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D27" t="str">
         <v>0.16</v>
@@ -12213,7 +12213,7 @@
         <v>2.159</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D28" t="str">
         <v>0.16</v>
@@ -12254,7 +12254,7 @@
         <v>2.240</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D29" t="str">
         <v>0.16</v>
@@ -12295,7 +12295,7 @@
         <v>2.325</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D30" t="str">
         <v>0.15</v>
@@ -12336,7 +12336,7 @@
         <v>2.407</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D31" t="str">
         <v>0.14</v>
@@ -12377,7 +12377,7 @@
         <v>2.491</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D32" t="str">
         <v>0.13</v>
@@ -12418,7 +12418,7 @@
         <v>2.573</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D33" t="str">
         <v>0.12</v>
@@ -12459,7 +12459,7 @@
         <v>2.656</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D34" t="str">
         <v>0.12</v>
@@ -12500,7 +12500,7 @@
         <v>2.739</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D35" t="str">
         <v>0.12</v>
@@ -12541,7 +12541,7 @@
         <v>2.823</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D36" t="str">
         <v>0.13</v>
@@ -12582,7 +12582,7 @@
         <v>2.905</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D37" t="str">
         <v>0.13</v>
@@ -12623,7 +12623,7 @@
         <v>2.988</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D38" t="str">
         <v>0.14</v>
@@ -12664,7 +12664,7 @@
         <v>3.071</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D39" t="str">
         <v>0.14</v>
@@ -12705,7 +12705,7 @@
         <v>3.152</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D40" t="str">
         <v>0.14</v>
@@ -12746,7 +12746,7 @@
         <v>3.237</v>
       </c>
       <c r="C41" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D41" t="str">
         <v>0.14</v>
@@ -12787,7 +12787,7 @@
         <v>3.320</v>
       </c>
       <c r="C42" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D42" t="str">
         <v>0.14</v>
@@ -12828,7 +12828,7 @@
         <v>3.403</v>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D43" t="str">
         <v>0.14</v>
@@ -12869,7 +12869,7 @@
         <v>3.483</v>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D44" t="str">
         <v>0.14</v>
@@ -12910,7 +12910,7 @@
         <v>3.570</v>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D45" t="str">
         <v>0.14</v>
@@ -12951,7 +12951,7 @@
         <v>3.652</v>
       </c>
       <c r="C46" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D46" t="str">
         <v>0.14</v>
@@ -12992,7 +12992,7 @@
         <v>3.735</v>
       </c>
       <c r="C47" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D47" t="str">
         <v>0.14</v>
@@ -13033,7 +13033,7 @@
         <v>3.818</v>
       </c>
       <c r="C48" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D48" t="str">
         <v>0.14</v>
@@ -13074,7 +13074,7 @@
         <v>3.902</v>
       </c>
       <c r="C49" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D49" t="str">
         <v>0.14</v>
@@ -13115,7 +13115,7 @@
         <v>3.984</v>
       </c>
       <c r="C50" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D50" t="str">
         <v>0.14</v>
@@ -13156,7 +13156,7 @@
         <v>4.067</v>
       </c>
       <c r="C51" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D51" t="str">
         <v>0.14</v>
@@ -13197,7 +13197,7 @@
         <v>4.150</v>
       </c>
       <c r="C52" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D52" t="str">
         <v>0.14</v>
@@ -13238,7 +13238,7 @@
         <v>4.232</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D53" t="str">
         <v>0.14</v>
@@ -13279,7 +13279,7 @@
         <v>4.316</v>
       </c>
       <c r="C54" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D54" t="str">
         <v>0.14</v>
@@ -13320,7 +13320,7 @@
         <v>4.399</v>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D55" t="str">
         <v>0.14</v>
@@ -13361,7 +13361,7 @@
         <v>4.483</v>
       </c>
       <c r="C56" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D56" t="str">
         <v>0.14</v>
@@ -13402,7 +13402,7 @@
         <v>4.565</v>
       </c>
       <c r="C57" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D57" t="str">
         <v>0.14</v>
@@ -13443,7 +13443,7 @@
         <v>4.648</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D58" t="str">
         <v>0.14</v>
@@ -13484,7 +13484,7 @@
         <v>4.731</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D59" t="str">
         <v>0.14</v>
@@ -13525,7 +13525,7 @@
         <v>4.814</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D60" t="str">
         <v>0.14</v>
@@ -13566,7 +13566,7 @@
         <v>4.898</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D61" t="str">
         <v>0.14</v>
@@ -13607,7 +13607,7 @@
         <v>4.981</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D62" t="str">
         <v>0.14</v>
@@ -13648,7 +13648,7 @@
         <v>5.061</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D63" t="str">
         <v>0.14</v>
@@ -13689,7 +13689,7 @@
         <v>5.147</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D64" t="str">
         <v>0.14</v>
@@ -13730,7 +13730,7 @@
         <v>5.228</v>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D65" t="str">
         <v>0.14</v>
@@ -13771,7 +13771,7 @@
         <v>5.312</v>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D66" t="str">
         <v>0.14</v>
@@ -13812,7 +13812,7 @@
         <v>5.394</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D67" t="str">
         <v>0.14</v>
@@ -13853,7 +13853,7 @@
         <v>5.478</v>
       </c>
       <c r="C68" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D68" t="str">
         <v>0.14</v>
@@ -13894,7 +13894,7 @@
         <v>5.561</v>
       </c>
       <c r="C69" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D69" t="str">
         <v>0.14</v>
@@ -13935,7 +13935,7 @@
         <v>5.645</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D70" t="str">
         <v>0.14</v>
@@ -13976,7 +13976,7 @@
         <v>5.727</v>
       </c>
       <c r="C71" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D71" t="str">
         <v>0.14</v>
@@ -14017,7 +14017,7 @@
         <v>5.810</v>
       </c>
       <c r="C72" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D72" t="str">
         <v>0.14</v>
@@ -14058,7 +14058,7 @@
         <v>5.894</v>
       </c>
       <c r="C73" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D73" t="str">
         <v>0.14</v>
@@ -14099,7 +14099,7 @@
         <v>5.975</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D74" t="str">
         <v>0.14</v>
@@ -14140,7 +14140,7 @@
         <v>6.059</v>
       </c>
       <c r="C75" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D75" t="str">
         <v>0.14</v>
@@ -14181,7 +14181,7 @@
         <v>6.144</v>
       </c>
       <c r="C76" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D76" t="str">
         <v>0.14</v>
@@ -14222,7 +14222,7 @@
         <v>6.225</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D77" t="str">
         <v>0.14</v>
@@ -14263,7 +14263,7 @@
         <v>6.308</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>(16, 1) (16, 5) (19, 5) (19, 1)</v>
       </c>
       <c r="D78" t="str">
         <v>0.14</v>
@@ -14309,7 +14309,7 @@
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
@@ -14330,7 +14330,7 @@
         <v>秒数(s)</v>
       </c>
       <c r="C1" t="str">
-        <v>框选坐标(JSON)</v>
+        <v>框选坐标</v>
       </c>
       <c r="D1" t="str">
         <v>上身框选3最大压强(N/cm²)</v>
@@ -14371,7 +14371,7 @@
         <v>0.000</v>
       </c>
       <c r="C2" t="str">
-        <v>{"key":"endi-jacket","xStart":11,"xEnd":15,"yStart":16,"yEnd":20,"width":24,"height":54,"name":"框选3","colorIndex":2}</v>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D2" t="str">
         <v>0.10</v>
@@ -14412,7 +14412,7 @@
         <v>0.084</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D3" t="str">
         <v>0.10</v>
@@ -14453,7 +14453,7 @@
         <v>0.166</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D4" t="str">
         <v>0.10</v>
@@ -14494,7 +14494,7 @@
         <v>0.249</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D5" t="str">
         <v>0.10</v>
@@ -14535,7 +14535,7 @@
         <v>0.333</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D6" t="str">
         <v>0.10</v>
@@ -14576,7 +14576,7 @@
         <v>0.415</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D7" t="str">
         <v>0.10</v>
@@ -14617,7 +14617,7 @@
         <v>0.499</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D8" t="str">
         <v>0.10</v>
@@ -14658,7 +14658,7 @@
         <v>0.582</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D9" t="str">
         <v>0.10</v>
@@ -14699,7 +14699,7 @@
         <v>0.664</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D10" t="str">
         <v>0.10</v>
@@ -14740,7 +14740,7 @@
         <v>0.747</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D11" t="str">
         <v>0.09</v>
@@ -14781,7 +14781,7 @@
         <v>0.831</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D12" t="str">
         <v>0.09</v>
@@ -14822,7 +14822,7 @@
         <v>0.913</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D13" t="str">
         <v>0.08</v>
@@ -14863,7 +14863,7 @@
         <v>0.997</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D14" t="str">
         <v>0.07</v>
@@ -14904,7 +14904,7 @@
         <v>1.080</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D15" t="str">
         <v>0.09</v>
@@ -14945,7 +14945,7 @@
         <v>1.162</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D16" t="str">
         <v>0.09</v>
@@ -14986,7 +14986,7 @@
         <v>1.244</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D17" t="str">
         <v>0.10</v>
@@ -15027,7 +15027,7 @@
         <v>1.328</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D18" t="str">
         <v>0.11</v>
@@ -15068,7 +15068,7 @@
         <v>1.411</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D19" t="str">
         <v>0.08</v>
@@ -15109,7 +15109,7 @@
         <v>1.494</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D20" t="str">
         <v>0.07</v>
@@ -15150,7 +15150,7 @@
         <v>1.576</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D21" t="str">
         <v>0.07</v>
@@ -15191,7 +15191,7 @@
         <v>1.660</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D22" t="str">
         <v>0.06</v>
@@ -15232,7 +15232,7 @@
         <v>1.743</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D23" t="str">
         <v>0.09</v>
@@ -15273,7 +15273,7 @@
         <v>1.826</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D24" t="str">
         <v>0.11</v>
@@ -15314,7 +15314,7 @@
         <v>1.910</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D25" t="str">
         <v>0.16</v>
@@ -15355,7 +15355,7 @@
         <v>1.990</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D26" t="str">
         <v>0.17</v>
@@ -15396,7 +15396,7 @@
         <v>2.076</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D27" t="str">
         <v>0.18</v>
@@ -15437,7 +15437,7 @@
         <v>2.159</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D28" t="str">
         <v>0.18</v>
@@ -15478,7 +15478,7 @@
         <v>2.240</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D29" t="str">
         <v>0.19</v>
@@ -15519,7 +15519,7 @@
         <v>2.325</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D30" t="str">
         <v>0.17</v>
@@ -15560,7 +15560,7 @@
         <v>2.407</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D31" t="str">
         <v>0.14</v>
@@ -15601,7 +15601,7 @@
         <v>2.491</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D32" t="str">
         <v>0.15</v>
@@ -15642,7 +15642,7 @@
         <v>2.573</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D33" t="str">
         <v>0.13</v>
@@ -15683,7 +15683,7 @@
         <v>2.656</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D34" t="str">
         <v>0.14</v>
@@ -15724,7 +15724,7 @@
         <v>2.739</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D35" t="str">
         <v>0.14</v>
@@ -15765,7 +15765,7 @@
         <v>2.823</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D36" t="str">
         <v>0.15</v>
@@ -15806,7 +15806,7 @@
         <v>2.905</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D37" t="str">
         <v>0.16</v>
@@ -15847,7 +15847,7 @@
         <v>2.988</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D38" t="str">
         <v>0.16</v>
@@ -15888,7 +15888,7 @@
         <v>3.071</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D39" t="str">
         <v>0.16</v>
@@ -15929,7 +15929,7 @@
         <v>3.152</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D40" t="str">
         <v>0.16</v>
@@ -15970,7 +15970,7 @@
         <v>3.237</v>
       </c>
       <c r="C41" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D41" t="str">
         <v>0.16</v>
@@ -16011,7 +16011,7 @@
         <v>3.320</v>
       </c>
       <c r="C42" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D42" t="str">
         <v>0.14</v>
@@ -16052,7 +16052,7 @@
         <v>3.403</v>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D43" t="str">
         <v>0.14</v>
@@ -16093,7 +16093,7 @@
         <v>3.483</v>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D44" t="str">
         <v>0.13</v>
@@ -16134,7 +16134,7 @@
         <v>3.570</v>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D45" t="str">
         <v>0.14</v>
@@ -16175,7 +16175,7 @@
         <v>3.652</v>
       </c>
       <c r="C46" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D46" t="str">
         <v>0.14</v>
@@ -16216,7 +16216,7 @@
         <v>3.735</v>
       </c>
       <c r="C47" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D47" t="str">
         <v>0.14</v>
@@ -16257,7 +16257,7 @@
         <v>3.818</v>
       </c>
       <c r="C48" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D48" t="str">
         <v>0.14</v>
@@ -16298,7 +16298,7 @@
         <v>3.902</v>
       </c>
       <c r="C49" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D49" t="str">
         <v>0.14</v>
@@ -16339,7 +16339,7 @@
         <v>3.984</v>
       </c>
       <c r="C50" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D50" t="str">
         <v>0.14</v>
@@ -16380,7 +16380,7 @@
         <v>4.067</v>
       </c>
       <c r="C51" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D51" t="str">
         <v>0.14</v>
@@ -16421,7 +16421,7 @@
         <v>4.150</v>
       </c>
       <c r="C52" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D52" t="str">
         <v>0.14</v>
@@ -16462,7 +16462,7 @@
         <v>4.232</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D53" t="str">
         <v>0.13</v>
@@ -16503,7 +16503,7 @@
         <v>4.316</v>
       </c>
       <c r="C54" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D54" t="str">
         <v>0.14</v>
@@ -16544,7 +16544,7 @@
         <v>4.399</v>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D55" t="str">
         <v>0.14</v>
@@ -16585,7 +16585,7 @@
         <v>4.483</v>
       </c>
       <c r="C56" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D56" t="str">
         <v>0.13</v>
@@ -16626,7 +16626,7 @@
         <v>4.565</v>
       </c>
       <c r="C57" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D57" t="str">
         <v>0.13</v>
@@ -16667,7 +16667,7 @@
         <v>4.648</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D58" t="str">
         <v>0.14</v>
@@ -16708,7 +16708,7 @@
         <v>4.731</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D59" t="str">
         <v>0.14</v>
@@ -16749,7 +16749,7 @@
         <v>4.814</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D60" t="str">
         <v>0.14</v>
@@ -16790,7 +16790,7 @@
         <v>4.898</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D61" t="str">
         <v>0.14</v>
@@ -16831,7 +16831,7 @@
         <v>4.981</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D62" t="str">
         <v>0.13</v>
@@ -16872,7 +16872,7 @@
         <v>5.061</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D63" t="str">
         <v>0.13</v>
@@ -16913,7 +16913,7 @@
         <v>5.147</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D64" t="str">
         <v>0.13</v>
@@ -16954,7 +16954,7 @@
         <v>5.228</v>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D65" t="str">
         <v>0.13</v>
@@ -16995,7 +16995,7 @@
         <v>5.312</v>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D66" t="str">
         <v>0.13</v>
@@ -17036,7 +17036,7 @@
         <v>5.394</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D67" t="str">
         <v>0.14</v>
@@ -17077,7 +17077,7 @@
         <v>5.478</v>
       </c>
       <c r="C68" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D68" t="str">
         <v>0.13</v>
@@ -17118,7 +17118,7 @@
         <v>5.561</v>
       </c>
       <c r="C69" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D69" t="str">
         <v>0.13</v>
@@ -17159,7 +17159,7 @@
         <v>5.645</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D70" t="str">
         <v>0.13</v>
@@ -17200,7 +17200,7 @@
         <v>5.727</v>
       </c>
       <c r="C71" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D71" t="str">
         <v>0.13</v>
@@ -17241,7 +17241,7 @@
         <v>5.810</v>
       </c>
       <c r="C72" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D72" t="str">
         <v>0.13</v>
@@ -17282,7 +17282,7 @@
         <v>5.894</v>
       </c>
       <c r="C73" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D73" t="str">
         <v>0.13</v>
@@ -17323,7 +17323,7 @@
         <v>5.975</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D74" t="str">
         <v>0.13</v>
@@ -17364,7 +17364,7 @@
         <v>6.059</v>
       </c>
       <c r="C75" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D75" t="str">
         <v>0.14</v>
@@ -17405,7 +17405,7 @@
         <v>6.144</v>
       </c>
       <c r="C76" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D76" t="str">
         <v>0.13</v>
@@ -17446,7 +17446,7 @@
         <v>6.225</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D77" t="str">
         <v>0.13</v>
@@ -17487,7 +17487,7 @@
         <v>6.308</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>(16, 11) (16, 14) (19, 14) (19, 11)</v>
       </c>
       <c r="D78" t="str">
         <v>0.14</v>
@@ -17533,7 +17533,7 @@
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
@@ -17554,7 +17554,7 @@
         <v>秒数(s)</v>
       </c>
       <c r="C1" t="str">
-        <v>框选坐标(JSON)</v>
+        <v>框选坐标</v>
       </c>
       <c r="D1" t="str">
         <v>上身框选4最大压强(N/cm²)</v>
@@ -17595,7 +17595,7 @@
         <v>0.000</v>
       </c>
       <c r="C2" t="str">
-        <v>{"key":"endi-jacket","xStart":7,"xEnd":10,"yStart":25,"yEnd":32,"width":24,"height":54,"name":"框选4","colorIndex":3}</v>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D2" t="str">
         <v>0.00</v>
@@ -17636,7 +17636,7 @@
         <v>0.084</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D3" t="str">
         <v>0.00</v>
@@ -17677,7 +17677,7 @@
         <v>0.166</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D4" t="str">
         <v>0.00</v>
@@ -17718,7 +17718,7 @@
         <v>0.249</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D5" t="str">
         <v>0.00</v>
@@ -17759,7 +17759,7 @@
         <v>0.333</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D6" t="str">
         <v>0.00</v>
@@ -17800,7 +17800,7 @@
         <v>0.415</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D7" t="str">
         <v>0.00</v>
@@ -17841,7 +17841,7 @@
         <v>0.499</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D8" t="str">
         <v>0.00</v>
@@ -17882,7 +17882,7 @@
         <v>0.582</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D9" t="str">
         <v>0.00</v>
@@ -17923,7 +17923,7 @@
         <v>0.664</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D10" t="str">
         <v>0.00</v>
@@ -17964,7 +17964,7 @@
         <v>0.747</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D11" t="str">
         <v>0.00</v>
@@ -18005,7 +18005,7 @@
         <v>0.831</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D12" t="str">
         <v>0.00</v>
@@ -18046,7 +18046,7 @@
         <v>0.913</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D13" t="str">
         <v>0.00</v>
@@ -18087,7 +18087,7 @@
         <v>0.997</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D14" t="str">
         <v>0.00</v>
@@ -18128,7 +18128,7 @@
         <v>1.080</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D15" t="str">
         <v>0.00</v>
@@ -18169,7 +18169,7 @@
         <v>1.162</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D16" t="str">
         <v>0.00</v>
@@ -18210,7 +18210,7 @@
         <v>1.244</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D17" t="str">
         <v>0.00</v>
@@ -18251,7 +18251,7 @@
         <v>1.328</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D18" t="str">
         <v>0.04</v>
@@ -18292,7 +18292,7 @@
         <v>1.411</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D19" t="str">
         <v>0.00</v>
@@ -18333,7 +18333,7 @@
         <v>1.494</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D20" t="str">
         <v>0.00</v>
@@ -18374,7 +18374,7 @@
         <v>1.576</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D21" t="str">
         <v>0.00</v>
@@ -18415,7 +18415,7 @@
         <v>1.660</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D22" t="str">
         <v>0.00</v>
@@ -18456,7 +18456,7 @@
         <v>1.743</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D23" t="str">
         <v>0.00</v>
@@ -18497,7 +18497,7 @@
         <v>1.826</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D24" t="str">
         <v>0.00</v>
@@ -18538,7 +18538,7 @@
         <v>1.910</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D25" t="str">
         <v>0.07</v>
@@ -18579,7 +18579,7 @@
         <v>1.990</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D26" t="str">
         <v>0.07</v>
@@ -18620,7 +18620,7 @@
         <v>2.076</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D27" t="str">
         <v>0.08</v>
@@ -18661,7 +18661,7 @@
         <v>2.159</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D28" t="str">
         <v>0.08</v>
@@ -18702,7 +18702,7 @@
         <v>2.240</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D29" t="str">
         <v>0.08</v>
@@ -18743,7 +18743,7 @@
         <v>2.325</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D30" t="str">
         <v>0.08</v>
@@ -18784,7 +18784,7 @@
         <v>2.407</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D31" t="str">
         <v>0.05</v>
@@ -18825,7 +18825,7 @@
         <v>2.491</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D32" t="str">
         <v>0.07</v>
@@ -18866,7 +18866,7 @@
         <v>2.573</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D33" t="str">
         <v>0.07</v>
@@ -18907,7 +18907,7 @@
         <v>2.656</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D34" t="str">
         <v>0.07</v>
@@ -18948,7 +18948,7 @@
         <v>2.739</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D35" t="str">
         <v>0.08</v>
@@ -18989,7 +18989,7 @@
         <v>2.823</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D36" t="str">
         <v>0.08</v>
@@ -19030,7 +19030,7 @@
         <v>2.905</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D37" t="str">
         <v>0.07</v>
@@ -19071,7 +19071,7 @@
         <v>2.988</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D38" t="str">
         <v>0.08</v>
@@ -19112,7 +19112,7 @@
         <v>3.071</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D39" t="str">
         <v>0.07</v>
@@ -19153,7 +19153,7 @@
         <v>3.152</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D40" t="str">
         <v>0.07</v>
@@ -19194,7 +19194,7 @@
         <v>3.237</v>
       </c>
       <c r="C41" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D41" t="str">
         <v>0.07</v>
@@ -19235,7 +19235,7 @@
         <v>3.320</v>
       </c>
       <c r="C42" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D42" t="str">
         <v>0.05</v>
@@ -19276,7 +19276,7 @@
         <v>3.403</v>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D43" t="str">
         <v>0.04</v>
@@ -19317,7 +19317,7 @@
         <v>3.483</v>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D44" t="str">
         <v>0.04</v>
@@ -19358,7 +19358,7 @@
         <v>3.570</v>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D45" t="str">
         <v>0.04</v>
@@ -19399,7 +19399,7 @@
         <v>3.652</v>
       </c>
       <c r="C46" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D46" t="str">
         <v>0.04</v>
@@ -19440,7 +19440,7 @@
         <v>3.735</v>
       </c>
       <c r="C47" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D47" t="str">
         <v>0.04</v>
@@ -19481,7 +19481,7 @@
         <v>3.818</v>
       </c>
       <c r="C48" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D48" t="str">
         <v>0.05</v>
@@ -19522,7 +19522,7 @@
         <v>3.902</v>
       </c>
       <c r="C49" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D49" t="str">
         <v>0.05</v>
@@ -19563,7 +19563,7 @@
         <v>3.984</v>
       </c>
       <c r="C50" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D50" t="str">
         <v>0.05</v>
@@ -19604,7 +19604,7 @@
         <v>4.067</v>
       </c>
       <c r="C51" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D51" t="str">
         <v>0.05</v>
@@ -19645,7 +19645,7 @@
         <v>4.150</v>
       </c>
       <c r="C52" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D52" t="str">
         <v>0.04</v>
@@ -19686,7 +19686,7 @@
         <v>4.232</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D53" t="str">
         <v>0.04</v>
@@ -19727,7 +19727,7 @@
         <v>4.316</v>
       </c>
       <c r="C54" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D54" t="str">
         <v>0.04</v>
@@ -19768,7 +19768,7 @@
         <v>4.399</v>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D55" t="str">
         <v>0.04</v>
@@ -19809,7 +19809,7 @@
         <v>4.483</v>
       </c>
       <c r="C56" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D56" t="str">
         <v>0.04</v>
@@ -19850,7 +19850,7 @@
         <v>4.565</v>
       </c>
       <c r="C57" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D57" t="str">
         <v>0.04</v>
@@ -19891,7 +19891,7 @@
         <v>4.648</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D58" t="str">
         <v>0.04</v>
@@ -19932,7 +19932,7 @@
         <v>4.731</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D59" t="str">
         <v>0.04</v>
@@ -19973,7 +19973,7 @@
         <v>4.814</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D60" t="str">
         <v>0.04</v>
@@ -20014,7 +20014,7 @@
         <v>4.898</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D61" t="str">
         <v>0.04</v>
@@ -20055,7 +20055,7 @@
         <v>4.981</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D62" t="str">
         <v>0.04</v>
@@ -20096,7 +20096,7 @@
         <v>5.061</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D63" t="str">
         <v>0.04</v>
@@ -20137,7 +20137,7 @@
         <v>5.147</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D64" t="str">
         <v>0.04</v>
@@ -20178,7 +20178,7 @@
         <v>5.228</v>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D65" t="str">
         <v>0.04</v>
@@ -20219,7 +20219,7 @@
         <v>5.312</v>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D66" t="str">
         <v>0.04</v>
@@ -20260,7 +20260,7 @@
         <v>5.394</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D67" t="str">
         <v>0.04</v>
@@ -20301,7 +20301,7 @@
         <v>5.478</v>
       </c>
       <c r="C68" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D68" t="str">
         <v>0.04</v>
@@ -20342,7 +20342,7 @@
         <v>5.561</v>
       </c>
       <c r="C69" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D69" t="str">
         <v>0.04</v>
@@ -20383,7 +20383,7 @@
         <v>5.645</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D70" t="str">
         <v>0.04</v>
@@ -20424,7 +20424,7 @@
         <v>5.727</v>
       </c>
       <c r="C71" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D71" t="str">
         <v>0.04</v>
@@ -20465,7 +20465,7 @@
         <v>5.810</v>
       </c>
       <c r="C72" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D72" t="str">
         <v>0.04</v>
@@ -20506,7 +20506,7 @@
         <v>5.894</v>
       </c>
       <c r="C73" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D73" t="str">
         <v>0.04</v>
@@ -20547,7 +20547,7 @@
         <v>5.975</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D74" t="str">
         <v>0.04</v>
@@ -20588,7 +20588,7 @@
         <v>6.059</v>
       </c>
       <c r="C75" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D75" t="str">
         <v>0.04</v>
@@ -20629,7 +20629,7 @@
         <v>6.144</v>
       </c>
       <c r="C76" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D76" t="str">
         <v>0.04</v>
@@ -20670,7 +20670,7 @@
         <v>6.225</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D77" t="str">
         <v>0.04</v>
@@ -20711,7 +20711,7 @@
         <v>6.308</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>(25, 7) (25, 9) (31, 9) (31, 7)</v>
       </c>
       <c r="D78" t="str">
         <v>0.04</v>
@@ -20757,7 +20757,7 @@
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
@@ -20778,7 +20778,7 @@
         <v>秒数(s)</v>
       </c>
       <c r="C1" t="str">
-        <v>框选坐标(JSON)</v>
+        <v>框选坐标</v>
       </c>
       <c r="D1" t="str">
         <v>上身框选5最大压强(N/cm²)</v>
@@ -20819,7 +20819,7 @@
         <v>0.000</v>
       </c>
       <c r="C2" t="str">
-        <v>{"key":"endi-jacket","xStart":14,"xEnd":18,"yStart":28,"yEnd":35,"width":24,"height":54,"name":"框选5","colorIndex":4}</v>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D2" t="str">
         <v>0.00</v>
@@ -20860,7 +20860,7 @@
         <v>0.084</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D3" t="str">
         <v>0.00</v>
@@ -20901,7 +20901,7 @@
         <v>0.166</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D4" t="str">
         <v>0.04</v>
@@ -20942,7 +20942,7 @@
         <v>0.249</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D5" t="str">
         <v>0.04</v>
@@ -20983,7 +20983,7 @@
         <v>0.333</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D6" t="str">
         <v>0.05</v>
@@ -21024,7 +21024,7 @@
         <v>0.415</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D7" t="str">
         <v>0.06</v>
@@ -21065,7 +21065,7 @@
         <v>0.499</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D8" t="str">
         <v>0.07</v>
@@ -21106,7 +21106,7 @@
         <v>0.582</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D9" t="str">
         <v>0.07</v>
@@ -21147,7 +21147,7 @@
         <v>0.664</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D10" t="str">
         <v>0.07</v>
@@ -21188,7 +21188,7 @@
         <v>0.747</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D11" t="str">
         <v>0.05</v>
@@ -21229,7 +21229,7 @@
         <v>0.831</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D12" t="str">
         <v>0.04</v>
@@ -21270,7 +21270,7 @@
         <v>0.913</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D13" t="str">
         <v>0.00</v>
@@ -21311,7 +21311,7 @@
         <v>0.997</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D14" t="str">
         <v>0.00</v>
@@ -21352,7 +21352,7 @@
         <v>1.080</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D15" t="str">
         <v>0.05</v>
@@ -21393,7 +21393,7 @@
         <v>1.162</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D16" t="str">
         <v>0.04</v>
@@ -21434,7 +21434,7 @@
         <v>1.244</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D17" t="str">
         <v>0.04</v>
@@ -21475,7 +21475,7 @@
         <v>1.328</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D18" t="str">
         <v>0.05</v>
@@ -21516,7 +21516,7 @@
         <v>1.411</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D19" t="str">
         <v>0.07</v>
@@ -21557,7 +21557,7 @@
         <v>1.494</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D20" t="str">
         <v>0.06</v>
@@ -21598,7 +21598,7 @@
         <v>1.576</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D21" t="str">
         <v>0.00</v>
@@ -21639,7 +21639,7 @@
         <v>1.660</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D22" t="str">
         <v>0.00</v>
@@ -21680,7 +21680,7 @@
         <v>1.743</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D23" t="str">
         <v>0.00</v>
@@ -21721,7 +21721,7 @@
         <v>1.826</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D24" t="str">
         <v>0.06</v>
@@ -21762,7 +21762,7 @@
         <v>1.910</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D25" t="str">
         <v>0.09</v>
@@ -21803,7 +21803,7 @@
         <v>1.990</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D26" t="str">
         <v>0.12</v>
@@ -21844,7 +21844,7 @@
         <v>2.076</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D27" t="str">
         <v>0.12</v>
@@ -21885,7 +21885,7 @@
         <v>2.159</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D28" t="str">
         <v>0.12</v>
@@ -21926,7 +21926,7 @@
         <v>2.240</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D29" t="str">
         <v>0.10</v>
@@ -21967,7 +21967,7 @@
         <v>2.325</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D30" t="str">
         <v>0.08</v>
@@ -22008,7 +22008,7 @@
         <v>2.407</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D31" t="str">
         <v>0.11</v>
@@ -22049,7 +22049,7 @@
         <v>2.491</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D32" t="str">
         <v>0.13</v>
@@ -22090,7 +22090,7 @@
         <v>2.573</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D33" t="str">
         <v>0.15</v>
@@ -22131,7 +22131,7 @@
         <v>2.656</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D34" t="str">
         <v>0.16</v>
@@ -22172,7 +22172,7 @@
         <v>2.739</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D35" t="str">
         <v>0.15</v>
@@ -22213,7 +22213,7 @@
         <v>2.823</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D36" t="str">
         <v>0.15</v>
@@ -22254,7 +22254,7 @@
         <v>2.905</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D37" t="str">
         <v>0.14</v>
@@ -22295,7 +22295,7 @@
         <v>2.988</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D38" t="str">
         <v>0.14</v>
@@ -22336,7 +22336,7 @@
         <v>3.071</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D39" t="str">
         <v>0.14</v>
@@ -22377,7 +22377,7 @@
         <v>3.152</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D40" t="str">
         <v>0.14</v>
@@ -22418,7 +22418,7 @@
         <v>3.237</v>
       </c>
       <c r="C41" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D41" t="str">
         <v>0.13</v>
@@ -22459,7 +22459,7 @@
         <v>3.320</v>
       </c>
       <c r="C42" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D42" t="str">
         <v>0.13</v>
@@ -22500,7 +22500,7 @@
         <v>3.403</v>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D43" t="str">
         <v>0.13</v>
@@ -22541,7 +22541,7 @@
         <v>3.483</v>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D44" t="str">
         <v>0.13</v>
@@ -22582,7 +22582,7 @@
         <v>3.570</v>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D45" t="str">
         <v>0.13</v>
@@ -22623,7 +22623,7 @@
         <v>3.652</v>
       </c>
       <c r="C46" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D46" t="str">
         <v>0.13</v>
@@ -22664,7 +22664,7 @@
         <v>3.735</v>
       </c>
       <c r="C47" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D47" t="str">
         <v>0.13</v>
@@ -22705,7 +22705,7 @@
         <v>3.818</v>
       </c>
       <c r="C48" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D48" t="str">
         <v>0.12</v>
@@ -22746,7 +22746,7 @@
         <v>3.902</v>
       </c>
       <c r="C49" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D49" t="str">
         <v>0.12</v>
@@ -22787,7 +22787,7 @@
         <v>3.984</v>
       </c>
       <c r="C50" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D50" t="str">
         <v>0.12</v>
@@ -22828,7 +22828,7 @@
         <v>4.067</v>
       </c>
       <c r="C51" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D51" t="str">
         <v>0.11</v>
@@ -22869,7 +22869,7 @@
         <v>4.150</v>
       </c>
       <c r="C52" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D52" t="str">
         <v>0.10</v>
@@ -22910,7 +22910,7 @@
         <v>4.232</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D53" t="str">
         <v>0.11</v>
@@ -22951,7 +22951,7 @@
         <v>4.316</v>
       </c>
       <c r="C54" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D54" t="str">
         <v>0.11</v>
@@ -22992,7 +22992,7 @@
         <v>4.399</v>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D55" t="str">
         <v>0.11</v>
@@ -23033,7 +23033,7 @@
         <v>4.483</v>
       </c>
       <c r="C56" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D56" t="str">
         <v>0.11</v>
@@ -23074,7 +23074,7 @@
         <v>4.565</v>
       </c>
       <c r="C57" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D57" t="str">
         <v>0.11</v>
@@ -23115,7 +23115,7 @@
         <v>4.648</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D58" t="str">
         <v>0.08</v>
@@ -23156,7 +23156,7 @@
         <v>4.731</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D59" t="str">
         <v>0.09</v>
@@ -23197,7 +23197,7 @@
         <v>4.814</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D60" t="str">
         <v>0.10</v>
@@ -23238,7 +23238,7 @@
         <v>4.898</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D61" t="str">
         <v>0.11</v>
@@ -23279,7 +23279,7 @@
         <v>4.981</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D62" t="str">
         <v>0.11</v>
@@ -23320,7 +23320,7 @@
         <v>5.061</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D63" t="str">
         <v>0.11</v>
@@ -23361,7 +23361,7 @@
         <v>5.147</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D64" t="str">
         <v>0.11</v>
@@ -23402,7 +23402,7 @@
         <v>5.228</v>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D65" t="str">
         <v>0.11</v>
@@ -23443,7 +23443,7 @@
         <v>5.312</v>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D66" t="str">
         <v>0.11</v>
@@ -23484,7 +23484,7 @@
         <v>5.394</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D67" t="str">
         <v>0.11</v>
@@ -23525,7 +23525,7 @@
         <v>5.478</v>
       </c>
       <c r="C68" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D68" t="str">
         <v>0.11</v>
@@ -23566,7 +23566,7 @@
         <v>5.561</v>
       </c>
       <c r="C69" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D69" t="str">
         <v>0.11</v>
@@ -23607,7 +23607,7 @@
         <v>5.645</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D70" t="str">
         <v>0.11</v>
@@ -23648,7 +23648,7 @@
         <v>5.727</v>
       </c>
       <c r="C71" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D71" t="str">
         <v>0.11</v>
@@ -23689,7 +23689,7 @@
         <v>5.810</v>
       </c>
       <c r="C72" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D72" t="str">
         <v>0.11</v>
@@ -23730,7 +23730,7 @@
         <v>5.894</v>
       </c>
       <c r="C73" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D73" t="str">
         <v>0.11</v>
@@ -23771,7 +23771,7 @@
         <v>5.975</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D74" t="str">
         <v>0.11</v>
@@ -23812,7 +23812,7 @@
         <v>6.059</v>
       </c>
       <c r="C75" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D75" t="str">
         <v>0.11</v>
@@ -23853,7 +23853,7 @@
         <v>6.144</v>
       </c>
       <c r="C76" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D76" t="str">
         <v>0.11</v>
@@ -23894,7 +23894,7 @@
         <v>6.225</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D77" t="str">
         <v>0.11</v>
@@ -23935,7 +23935,7 @@
         <v>6.308</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>(28, 14) (28, 17) (34, 17) (34, 14)</v>
       </c>
       <c r="D78" t="str">
         <v>0.11</v>
@@ -23981,7 +23981,7 @@
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
@@ -24002,7 +24002,7 @@
         <v>秒数(s)</v>
       </c>
       <c r="C1" t="str">
-        <v>框选坐标(JSON)</v>
+        <v>框选坐标</v>
       </c>
       <c r="D1" t="str">
         <v>上身框选6最大压强(N/cm²)</v>
@@ -24043,7 +24043,7 @@
         <v>0.000</v>
       </c>
       <c r="C2" t="str">
-        <v>{"key":"endi-jacket","xStart":5,"xEnd":14,"yStart":40,"yEnd":50,"width":24,"height":54,"name":"框选6","colorIndex":5}</v>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D2" t="str">
         <v>0.08</v>
@@ -24084,7 +24084,7 @@
         <v>0.084</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D3" t="str">
         <v>0.08</v>
@@ -24125,7 +24125,7 @@
         <v>0.166</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D4" t="str">
         <v>0.08</v>
@@ -24166,7 +24166,7 @@
         <v>0.249</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D5" t="str">
         <v>0.08</v>
@@ -24207,7 +24207,7 @@
         <v>0.333</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D6" t="str">
         <v>0.08</v>
@@ -24248,7 +24248,7 @@
         <v>0.415</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D7" t="str">
         <v>0.08</v>
@@ -24289,7 +24289,7 @@
         <v>0.499</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D8" t="str">
         <v>0.11</v>
@@ -24330,7 +24330,7 @@
         <v>0.582</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D9" t="str">
         <v>0.12</v>
@@ -24371,7 +24371,7 @@
         <v>0.664</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D10" t="str">
         <v>0.14</v>
@@ -24412,7 +24412,7 @@
         <v>0.747</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D11" t="str">
         <v>0.10</v>
@@ -24453,7 +24453,7 @@
         <v>0.831</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D12" t="str">
         <v>0.12</v>
@@ -24494,7 +24494,7 @@
         <v>0.913</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D13" t="str">
         <v>0.19</v>
@@ -24535,7 +24535,7 @@
         <v>0.997</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D14" t="str">
         <v>0.27</v>
@@ -24576,7 +24576,7 @@
         <v>1.080</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D15" t="str">
         <v>0.43</v>
@@ -24617,7 +24617,7 @@
         <v>1.162</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D16" t="str">
         <v>0.45</v>
@@ -24658,7 +24658,7 @@
         <v>1.244</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D17" t="str">
         <v>0.49</v>
@@ -24699,7 +24699,7 @@
         <v>1.328</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D18" t="str">
         <v>0.50</v>
@@ -24740,7 +24740,7 @@
         <v>1.411</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D19" t="str">
         <v>0.35</v>
@@ -24781,7 +24781,7 @@
         <v>1.494</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D20" t="str">
         <v>0.25</v>
@@ -24822,7 +24822,7 @@
         <v>1.576</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D21" t="str">
         <v>0.15</v>
@@ -24863,7 +24863,7 @@
         <v>1.660</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D22" t="str">
         <v>0.24</v>
@@ -24904,7 +24904,7 @@
         <v>1.743</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D23" t="str">
         <v>0.43</v>
@@ -24945,7 +24945,7 @@
         <v>1.826</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D24" t="str">
         <v>0.48</v>
@@ -24986,7 +24986,7 @@
         <v>1.910</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D25" t="str">
         <v>0.79</v>
@@ -25027,7 +25027,7 @@
         <v>1.990</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D26" t="str">
         <v>0.82</v>
@@ -25068,7 +25068,7 @@
         <v>2.076</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D27" t="str">
         <v>0.79</v>
@@ -25109,7 +25109,7 @@
         <v>2.159</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D28" t="str">
         <v>0.81</v>
@@ -25150,7 +25150,7 @@
         <v>2.240</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D29" t="str">
         <v>0.79</v>
@@ -25191,7 +25191,7 @@
         <v>2.325</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D30" t="str">
         <v>0.90</v>
@@ -25232,7 +25232,7 @@
         <v>2.407</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D31" t="str">
         <v>0.53</v>
@@ -25273,7 +25273,7 @@
         <v>2.491</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D32" t="str">
         <v>0.92</v>
@@ -25314,7 +25314,7 @@
         <v>2.573</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D33" t="str">
         <v>0.72</v>
@@ -25355,7 +25355,7 @@
         <v>2.656</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D34" t="str">
         <v>0.71</v>
@@ -25396,7 +25396,7 @@
         <v>2.739</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D35" t="str">
         <v>0.69</v>
@@ -25437,7 +25437,7 @@
         <v>2.823</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D36" t="str">
         <v>0.67</v>
@@ -25478,7 +25478,7 @@
         <v>2.905</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D37" t="str">
         <v>0.69</v>
@@ -25519,7 +25519,7 @@
         <v>2.988</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D38" t="str">
         <v>0.68</v>
@@ -25560,7 +25560,7 @@
         <v>3.071</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D39" t="str">
         <v>0.67</v>
@@ -25601,7 +25601,7 @@
         <v>3.152</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D40" t="str">
         <v>0.64</v>
@@ -25642,7 +25642,7 @@
         <v>3.237</v>
       </c>
       <c r="C41" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D41" t="str">
         <v>0.61</v>
@@ -25683,7 +25683,7 @@
         <v>3.320</v>
       </c>
       <c r="C42" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D42" t="str">
         <v>0.47</v>
@@ -25724,7 +25724,7 @@
         <v>3.403</v>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D43" t="str">
         <v>0.47</v>
@@ -25765,7 +25765,7 @@
         <v>3.483</v>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D44" t="str">
         <v>0.46</v>
@@ -25806,7 +25806,7 @@
         <v>3.570</v>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D45" t="str">
         <v>0.47</v>
@@ -25847,7 +25847,7 @@
         <v>3.652</v>
       </c>
       <c r="C46" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D46" t="str">
         <v>0.47</v>
@@ -25888,7 +25888,7 @@
         <v>3.735</v>
       </c>
       <c r="C47" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D47" t="str">
         <v>0.46</v>
@@ -25929,7 +25929,7 @@
         <v>3.818</v>
       </c>
       <c r="C48" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D48" t="str">
         <v>0.47</v>
@@ -25970,7 +25970,7 @@
         <v>3.902</v>
       </c>
       <c r="C49" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D49" t="str">
         <v>0.47</v>
@@ -26011,7 +26011,7 @@
         <v>3.984</v>
       </c>
       <c r="C50" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D50" t="str">
         <v>0.47</v>
@@ -26052,7 +26052,7 @@
         <v>4.067</v>
       </c>
       <c r="C51" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D51" t="str">
         <v>0.47</v>
@@ -26093,7 +26093,7 @@
         <v>4.150</v>
       </c>
       <c r="C52" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D52" t="str">
         <v>0.48</v>
@@ -26134,7 +26134,7 @@
         <v>4.232</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D53" t="str">
         <v>0.47</v>
@@ -26175,7 +26175,7 @@
         <v>4.316</v>
       </c>
       <c r="C54" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D54" t="str">
         <v>0.47</v>
@@ -26216,7 +26216,7 @@
         <v>4.399</v>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D55" t="str">
         <v>0.47</v>
@@ -26257,7 +26257,7 @@
         <v>4.483</v>
       </c>
       <c r="C56" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D56" t="str">
         <v>0.47</v>
@@ -26298,7 +26298,7 @@
         <v>4.565</v>
       </c>
       <c r="C57" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D57" t="str">
         <v>0.47</v>
@@ -26339,7 +26339,7 @@
         <v>4.648</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D58" t="str">
         <v>0.47</v>
@@ -26380,7 +26380,7 @@
         <v>4.731</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D59" t="str">
         <v>0.47</v>
@@ -26421,7 +26421,7 @@
         <v>4.814</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D60" t="str">
         <v>0.47</v>
@@ -26462,7 +26462,7 @@
         <v>4.898</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D61" t="str">
         <v>0.46</v>
@@ -26503,7 +26503,7 @@
         <v>4.981</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D62" t="str">
         <v>0.46</v>
@@ -26544,7 +26544,7 @@
         <v>5.061</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D63" t="str">
         <v>0.46</v>
@@ -26585,7 +26585,7 @@
         <v>5.147</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D64" t="str">
         <v>0.45</v>
@@ -26626,7 +26626,7 @@
         <v>5.228</v>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D65" t="str">
         <v>0.45</v>
@@ -26667,7 +26667,7 @@
         <v>5.312</v>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D66" t="str">
         <v>0.45</v>
@@ -26708,7 +26708,7 @@
         <v>5.394</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D67" t="str">
         <v>0.45</v>
@@ -26749,7 +26749,7 @@
         <v>5.478</v>
       </c>
       <c r="C68" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D68" t="str">
         <v>0.45</v>
@@ -26790,7 +26790,7 @@
         <v>5.561</v>
       </c>
       <c r="C69" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D69" t="str">
         <v>0.45</v>
@@ -26831,7 +26831,7 @@
         <v>5.645</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D70" t="str">
         <v>0.45</v>
@@ -26872,7 +26872,7 @@
         <v>5.727</v>
       </c>
       <c r="C71" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D71" t="str">
         <v>0.45</v>
@@ -26913,7 +26913,7 @@
         <v>5.810</v>
       </c>
       <c r="C72" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D72" t="str">
         <v>0.45</v>
@@ -26954,7 +26954,7 @@
         <v>5.894</v>
       </c>
       <c r="C73" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D73" t="str">
         <v>0.45</v>
@@ -26995,7 +26995,7 @@
         <v>5.975</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D74" t="str">
         <v>0.45</v>
@@ -27036,7 +27036,7 @@
         <v>6.059</v>
       </c>
       <c r="C75" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D75" t="str">
         <v>0.45</v>
@@ -27077,7 +27077,7 @@
         <v>6.144</v>
       </c>
       <c r="C76" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D76" t="str">
         <v>0.45</v>
@@ -27118,7 +27118,7 @@
         <v>6.225</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D77" t="str">
         <v>0.45</v>
@@ -27159,7 +27159,7 @@
         <v>6.308</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>(40, 5) (40, 13) (49, 13) (49, 5)</v>
       </c>
       <c r="D78" t="str">
         <v>0.45</v>
